--- a/artfynd/A 62726-2025 artfynd.xlsx
+++ b/artfynd/A 62726-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130330460</v>
       </c>
       <c r="B2" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>130331339</v>
       </c>
       <c r="B3" t="n">
-        <v>91749</v>
+        <v>91752</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>130339302</v>
       </c>
       <c r="B5" t="n">
-        <v>96158</v>
+        <v>96161</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>130408470</v>
       </c>
       <c r="B7" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 62726-2025 artfynd.xlsx
+++ b/artfynd/A 62726-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130330460</v>
       </c>
       <c r="B2" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>130331339</v>
       </c>
       <c r="B3" t="n">
-        <v>91752</v>
+        <v>91778</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>130339304</v>
       </c>
       <c r="B4" t="n">
-        <v>58198</v>
+        <v>58224</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>130339302</v>
       </c>
       <c r="B5" t="n">
-        <v>96161</v>
+        <v>96187</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>130339303</v>
       </c>
       <c r="B6" t="n">
-        <v>58198</v>
+        <v>58224</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>130408470</v>
       </c>
       <c r="B7" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>130339297</v>
       </c>
       <c r="B8" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 62726-2025 artfynd.xlsx
+++ b/artfynd/A 62726-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>130331339</v>
       </c>
       <c r="B3" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>130339302</v>
       </c>
       <c r="B5" t="n">
-        <v>96187</v>
+        <v>96188</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>130408470</v>
       </c>
       <c r="B7" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 62726-2025 artfynd.xlsx
+++ b/artfynd/A 62726-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>130331339</v>
       </c>
       <c r="B3" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>130339302</v>
       </c>
       <c r="B5" t="n">
-        <v>96188</v>
+        <v>96189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>130408470</v>
       </c>
       <c r="B7" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 62726-2025 artfynd.xlsx
+++ b/artfynd/A 62726-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130330460</v>
       </c>
       <c r="B2" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>130331339</v>
       </c>
       <c r="B3" t="n">
-        <v>91780</v>
+        <v>91782</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>130339304</v>
       </c>
       <c r="B4" t="n">
-        <v>58224</v>
+        <v>58226</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>130339302</v>
       </c>
       <c r="B5" t="n">
-        <v>96189</v>
+        <v>96191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>130339303</v>
       </c>
       <c r="B6" t="n">
-        <v>58224</v>
+        <v>58226</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>130408470</v>
       </c>
       <c r="B7" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>130339297</v>
       </c>
       <c r="B8" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 62726-2025 artfynd.xlsx
+++ b/artfynd/A 62726-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>130339302</v>
       </c>
       <c r="B5" t="n">
-        <v>96191</v>
+        <v>96195</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 62726-2025 artfynd.xlsx
+++ b/artfynd/A 62726-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1419,6 +1419,130 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131584750</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58051</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skogslund, 400 m. NNV., Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>483533</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6331587</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Asa</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>I äldre, flerskiktad barrskog.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Uno Pettersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Uno Pettersson, Per Fogelström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62726-2025 artfynd.xlsx
+++ b/artfynd/A 62726-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130330460</v>
+        <v>130408470</v>
       </c>
       <c r="B2" t="n">
-        <v>79221</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,48 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skogslund 400 m. NV, Sm</t>
+          <t>Skogslund, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483323</v>
+        <v>483517</v>
       </c>
       <c r="R2" t="n">
-        <v>6331555</v>
+        <v>6331625</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,11 +749,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-12-28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Kärrkant i äldre barrskog. Minst en bål.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,71 +764,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Uno Pettersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Uno Pettersson, Elin Kannerby</t>
+          <t>Elin Kannerby, Uno Pettersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130331339</v>
+        <v>130339302</v>
       </c>
       <c r="B3" t="n">
-        <v>91797</v>
+        <v>96350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>2813</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skogslund 450 m. NV, Sm</t>
+          <t>Skogslund, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483367</v>
+        <v>483334</v>
       </c>
       <c r="R3" t="n">
-        <v>6331698</v>
+        <v>6331500</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,86 +849,83 @@
           <t>2025-12-28</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På gammal tall i gran- tallskog. På en meters höjd.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Uno Pettersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Uno Pettersson, Elin Kannerby</t>
+          <t>Elin Kannerby, Uno Pettersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130339304</v>
+        <v>130331339</v>
       </c>
       <c r="B4" t="n">
-        <v>58236</v>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skogslund, Sm</t>
+          <t>Skogslund 450 m. NV, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483441</v>
+        <v>483367</v>
       </c>
       <c r="R4" t="n">
-        <v>6331686</v>
+        <v>6331698</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,72 +957,89 @@
           <t>2025-12-28</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På gammal tall i gran- tallskog. På en meters höjd.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Uno Pettersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Uno Pettersson</t>
+          <t>Uno Pettersson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130339302</v>
+        <v>130330460</v>
       </c>
       <c r="B5" t="n">
-        <v>96212</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2813</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skogslund, Sm</t>
+          <t>Skogslund 400 m. NV, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483334</v>
+        <v>483323</v>
       </c>
       <c r="R5" t="n">
-        <v>6331500</v>
+        <v>6331555</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,34 +1071,40 @@
           <t>2025-12-28</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Kärrkant i äldre barrskog. Minst en bål.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Uno Pettersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Uno Pettersson</t>
+          <t>Uno Pettersson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130339303</v>
+        <v>130339297</v>
       </c>
       <c r="B6" t="n">
-        <v>58236</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1116,16 +1112,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1138,7 +1134,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1148,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483296</v>
+        <v>483315</v>
       </c>
       <c r="R6" t="n">
-        <v>6331631</v>
+        <v>6331510</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,6 +1180,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Fanns flera spår efter spillkråka i hela området med hackmärken i basen av träd där den har födosökt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,37 +1211,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130408470</v>
+        <v>130339303</v>
       </c>
       <c r="B7" t="n">
-        <v>91798</v>
+        <v>58327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1248,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483517</v>
+        <v>483296</v>
       </c>
       <c r="R7" t="n">
-        <v>6331625</v>
+        <v>6331631</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,7 +1298,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1311,27 +1316,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130339297</v>
+        <v>130339304</v>
       </c>
       <c r="B8" t="n">
-        <v>57875</v>
+        <v>58327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1344,7 +1349,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1354,10 +1359,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483315</v>
+        <v>483441</v>
       </c>
       <c r="R8" t="n">
-        <v>6331510</v>
+        <v>6331686</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,11 +1395,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-28</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Fanns flera spår efter spillkråka i hela området med hackmärken i basen av träd där den har födosökt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1424,7 @@
         <v>131584750</v>
       </c>
       <c r="B9" t="n">
-        <v>58073</v>
+        <v>58136</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
